--- a/光伏配储项目/电价数据/2026/泷州站.xlsx
+++ b/光伏配储项目/电价数据/2026/泷州站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50975</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38509</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7404299999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57089</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5715</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.49615</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.49112</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43753</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45434</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43854</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41907</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40873</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39803</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40193</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42306</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41252</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41692</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42062</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41281</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44382</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27618</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.28482</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11114</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09063</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.09641</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.08116</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.10521</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.04118</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.08137</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.09476000000000001</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.09354999999999999</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.06966</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08931</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05936</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.04625</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.00076</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14656</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21418</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23667</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.24897</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.19893</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.06534999999999999</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00302</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.12798</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.26212</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.26177</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29174</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.25427</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.17641</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.27027</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.50559</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.45575</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.78431</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.5761000000000001</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42582</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43848</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.41458</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5629500000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.43667</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.5854</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.78971</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6335700000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.59981</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.70412</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.7510599999999999</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41429</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.65235</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5991799999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.62174</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.57245</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.56224</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6293200000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.59903</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.46387</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48465</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4159</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42552</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.68083</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.57876</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.75314</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.13039</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8094</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.52512</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51974</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50548</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50743</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49148</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47074</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41999</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59882</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.67601</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43128</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.40658</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.49926</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.14365</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.03472</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.46422</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7454700000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.85493</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.71888</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.47306</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.09941</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28162</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.45516</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.25835</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.30133</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.23941</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.25175</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.44515</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.40967</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29245</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.51928</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.6395700000000001</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.4937</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6846100000000001</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.74675</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.48868</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.47651</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.80036</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.47805</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.85292</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.44453</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.58468</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43869</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43238</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40946</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37767</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3345</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5222100000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.46423</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40131</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.38687</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43229</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44832</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39597</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36841</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38422</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.4739</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44826</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44258</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39705</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.28585</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.18935</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26516</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.29634</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.46149</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.39251</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.49718</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.46809</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.1411</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.24286</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.27481</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.27552</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29343</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28212</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.39513</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.39169</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.43538</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.41611</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.46631</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.49556</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.5834</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.47328</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5878099999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.43609</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.40306</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.4487</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.42529</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.44606</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.43231</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.40322</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.38435</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.38838</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34258</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.3979</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46006</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38953</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26557</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.14433</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.19923</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.14775</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.24703</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.1981</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.50701</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.04759</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.10377</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.29147</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28706</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.14692</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.15442</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.48323</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.04915</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.11529</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.20677</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.2319</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.23159</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.24824</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.21973</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.27706</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14981</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.2719</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.28315</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41696</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.54698</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.45206</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.44513</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29447</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29894</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29681</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29653</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.36684</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38278</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29462</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30593</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29926</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29031</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29031</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27957</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26086</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04314</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04711</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04315</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04882</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04764</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04901</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03534</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04759</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04412</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04165</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.03938000000000001</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.03997</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04103</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04056</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.03825</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04227</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04577000000000001</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04087</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04184</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04308</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04333</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04692</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04118</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21932</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04916</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05494</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05585</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.0012</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14934</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.04013000000000001</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.10084</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29244</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.38448</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40807</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.42374</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46768</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39657</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4175</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35118</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6657000000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44699</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42404</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42415</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10249</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04321</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04679</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04568999999999999</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04597</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04597</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04597</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04359</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03062</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.0419</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10672</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-7.000000000000001e-05</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03754</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04288</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04344</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04344</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04323</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04284</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04509000000000001</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04283</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04081</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04513</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04492</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04508</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04312</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04385</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04006000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04211</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04443</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04722</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04751</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20035</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14316</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29057</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29747</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29132</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29548</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26933</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36557</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.336</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31844</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40524</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30188</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28164</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28144</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27164</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27146</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28151</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17275</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15899</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17138</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14807</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15899</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2368</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21441</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22695</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26949</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28625</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28144</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28152</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27062</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29287</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38247</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42689</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45205</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41682</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41361</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40109</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15673</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50763</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62201</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49793</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78098</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.9203</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49449</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91738</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.87301</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.30155</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8972599999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63325</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19668</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87348</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.55053</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.34069</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03967</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5406599999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79938</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53098</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7814099999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78423</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87781</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87827</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50103</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40637</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41006</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45896</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21716</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87918</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55123</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6319199999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5408500000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50061</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45708</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42547</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43895</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39074</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45284</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42041</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38773</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41498</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43402</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40561</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45093</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40047</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58749</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42833</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59635</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60245</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6696</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46502</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.57726</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.87613</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6352899999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8505199999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.8323400000000001</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.85977</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.4397799999999999</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.43846</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27728</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41053</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41319</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45306</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41555</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35354</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.93632</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47127</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.38354</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.44409</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.5037200000000001</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41027</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.38966</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40064</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50092</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37099</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28943</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28622</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16485</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.29865</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26186</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19947</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27733</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.20951</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29319</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29058</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2556</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27623</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38588</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4367</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42324</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44872</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42086</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40217</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40092</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59814</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8904500000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.32615</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13191</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69533</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78431</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6474500000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57875</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.4491</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44828</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49739</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43784</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.4357</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.4134</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41131</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42196</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49809</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43211</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41185</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.4318</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42662</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44872</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39498</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42169</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43262</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41127</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42223</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40056</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.50171</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29667</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36537</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.55802</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24998</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.54195</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.24865</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.28569</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.10955</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.39801</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26278</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25692</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.27922</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29325</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39852</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39903</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57664</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46165</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46284</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43795</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42372</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38641</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36937</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32462</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42206</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39943</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37468</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28012</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23039</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14538</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.1495</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28749</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15704</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14538</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14167</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14519</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14214</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.26013</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.1457</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26905</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26115</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14384</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.11199</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11354</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10723</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.13665</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14064</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14529</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28094</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36396</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39715</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44838</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39919</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40103</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39685</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44344</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43839</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43771</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44256</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44224</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39676</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39069</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5373</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46626</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42202</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41421</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37939</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28925</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26606</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26113</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19454</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2468</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.23827</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26533</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28449</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29747</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23797</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.39761</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.2578</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41793</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35998</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.43052</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39703</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.44288</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43219</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.00521</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25055</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.25685</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.08902</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.21419</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25353</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.29324</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.27421</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44616</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44695</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71111</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.51528</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.29108</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.37278</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40482</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34968</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.41462</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38116</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43679</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41018</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6752899999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.78762</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47215</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45783</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34819</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41551</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38639</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26495</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14586</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28392</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19862</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25676</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27991</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.2183</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26205</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28483</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27812</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29115</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.15001</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29311</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29489</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43306</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.4241</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6209600000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.64975</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.67367</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.49012</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7358899999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.5200199999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.87664</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.46879</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48217</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.4080299999999999</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48348</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43078</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42833</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36019</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.4913</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.55045</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.49724</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42142</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40279</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40738</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41524</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40967</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41898</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41405</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40695</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39331</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38636</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41676</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41876</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38884</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40164</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40159</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41416</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40295</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44787</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45504</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5617000000000001</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49688</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44803</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.5508</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4611</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44093</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.4242</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.51548</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.44735</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29702</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36439</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28753</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.64015</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.15703</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.27992</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41001</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43322</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48864</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43548</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.51052</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.53523</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.60025</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.76712</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.78355</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.95392</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.71576</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80263</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.59553</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.54779</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.90637</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.8318</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62815</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.69813</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44945</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4709100000000001</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.50152</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47848</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.48858</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41846</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5624600000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.4288</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44351</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.4663</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45032</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.43108</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45451</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.42874</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40022</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.46701</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40706</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.4065299999999999</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.3872</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37383</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.39348</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40568</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39727</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.18136</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.37848</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40557</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44962</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39176</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46467</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.1108</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18116</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37813</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37273</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38963</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41557</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42691</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41206</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41112</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.3816000000000001</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40897</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40801</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37515</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36568</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44509</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39259</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37901</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.2701</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22872</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28892</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23076</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28901</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25058</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25326</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.1397</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29246</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.2501</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04339</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25183</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28771</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16893</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18077</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27278</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22756</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24787</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26134</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.2314</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27506</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28432</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28216</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35082</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.26525</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.25277</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.21365</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.20771</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01779</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00021</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.02648</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.0498</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.10912</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01289</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.0398</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0498</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.02291</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04525999999999999</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04913</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04887</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.0271</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03347</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04982</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.11198</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04981</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04981</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0497</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00271</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28795</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04981</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03254</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0498</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04986</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04273</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17105</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20434</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.24184</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27944</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26953</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.27113</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.27052</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27514</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.2906</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28449</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41081</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.29781</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29835</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29096</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.16161</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.60178</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.18971</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30412</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.28215</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.28583</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.26161</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.25293</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.27789</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.26666</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.26485</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.25767</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.28833</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.28064</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.26378</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28736</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.3732799999999999</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28699</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.2427</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.18683</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6640900000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.67095</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.6782699999999999</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.6012000000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.17756</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09320999999999999</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.24456</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.19054</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.14249</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.14792</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.10737</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.23316</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.13088</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.04837</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.07102</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.1202</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.18718</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.0237</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.1404</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.16369</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.0092</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.1239</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.12896</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.13044</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.15978</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25315</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29202</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27316</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37387</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32394</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.09009</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.47509</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.54127</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.41088</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41137</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.41542</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.45523</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.45423</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.4378</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.13907</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.2737</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27005</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.27788</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29137</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.43661</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.41414</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33277</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37589</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.28869</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36948</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.60025</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.57653</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.5257000000000001</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26043</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.2815299999999999</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28295</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41415</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39852</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.50229</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.5154299999999999</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.45087</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.46158</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.43469</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.39919</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37321</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.39211</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.39068</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.39157</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.46963</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.4038</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.47739</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.41173</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38748</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.41148</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>1.60511</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37273</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.49818</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.37432</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47797</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.38542</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.3742200000000001</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36907</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40827</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.42901</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.2641</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37707</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29373</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.37971</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38752</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.46394</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.44259</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42621</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.4256</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5089900000000001</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5938099999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.59115</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39657</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46549</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5787100000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5097</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5577000000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5247200000000001</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.40944</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.56802</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.5275299999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.95727</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.85573</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.59772</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.59314</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.40678</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.45844</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.40764</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3789</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27158</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.24606</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.27413</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.28321</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.12344</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.20866</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.18221</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.05470000000000001</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.27986</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.12875</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.02303</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.19369</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16273</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.00447</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25471</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.15346</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05123</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04702000000000001</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.0602</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.1452</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.06839000000000001</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05185</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.16947</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.13703</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.16344</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.26065</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.29664</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.28281</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36403</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.2629</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39602</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4076</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41915</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42301</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38975</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42303</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.44371</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.39519</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37214</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.5079900000000001</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38044</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.9644400000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.48204</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.43206</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.38029</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38846</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37835</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36267</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38246</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.27737</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.27098</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.28192</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.27252</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11478</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01808</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01817</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01724</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03789</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.17597</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03961</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.006019999999999999</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01807</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04543</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01423</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01248</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.0142</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.16103</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.2607</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04406</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.24604</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.16067</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.25701</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.30598</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.47928</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41666</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40606</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36516</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39198</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5485599999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.5608099999999999</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39038</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39541</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.37244</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40093</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39914</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42372</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39406</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36787</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.37398</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37553</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.58985</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.43729</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28618</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23745</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14789</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.21521</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.23879</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.24266</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11769</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15628</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.05061</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.04292</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04781000000000001</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04661999999999999</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04682</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04432</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04179</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.08127</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02884</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06520000000000001</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.10036</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17749</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.20215</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12458</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.27059</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.23737</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12761</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04869</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26821</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.15248</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.1201</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.24156</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.19358</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.25082</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.25383</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.21147</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.28717</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38776</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.36948</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38807</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.50678</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40157</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.40999</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.41154</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.40426</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40812</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38452</v>
       </c>
     </row>
   </sheetData>
